--- a/data/employees/EMP086/AST-EMP086-06.xlsx
+++ b/data/employees/EMP086/AST-EMP086-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Avery Wilson (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Specialist | Location: Austin | Date: 2025-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP086</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp086 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>72</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP086</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp086 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>88</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP086</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp086 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>83</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP086</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp086 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>70</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>61</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>95</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>65</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>98</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>99</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>73</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>86</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>67</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>72</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>83</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>67</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>92</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp086 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>91</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP086</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP086 contributes to ast emp086 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>